--- a/IrregularVerbs-Ahorcado/irregular_verbs_full_list.xlsx
+++ b/IrregularVerbs-Ahorcado/irregular_verbs_full_list.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4506"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Valentina\Documents\_La.Miranda\_definitivos\GitHub\LucYago_Games\Irregular-Verbs-iPhone-AHORCADO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12480"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Verbs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
@@ -1182,8 +1177,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1531,9 +1526,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1546,7 +1541,7 @@
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +1573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1610,7 +1605,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1642,7 +1637,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1674,7 +1669,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="1" customFormat="1">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -1706,7 +1701,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="1" customFormat="1">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -1738,7 +1733,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="1" customFormat="1">
       <c r="A7" s="1" t="s">
         <v>52</v>
       </c>
@@ -1770,7 +1765,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="1" customFormat="1">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -1802,7 +1797,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="1" customFormat="1">
       <c r="A9" s="1" t="s">
         <v>66</v>
       </c>
@@ -1834,7 +1829,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="1" customFormat="1">
       <c r="A10" s="1" t="s">
         <v>74</v>
       </c>
@@ -1866,7 +1861,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="1" customFormat="1">
       <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
@@ -1895,7 +1890,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="1" customFormat="1">
       <c r="A12" s="1" t="s">
         <v>87</v>
       </c>
@@ -1927,7 +1922,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="1" customFormat="1">
       <c r="A13" s="1" t="s">
         <v>95</v>
       </c>
@@ -1959,7 +1954,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="1" customFormat="1">
       <c r="A14" s="1" t="s">
         <v>101</v>
       </c>
@@ -1991,7 +1986,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="1" customFormat="1">
       <c r="A15" s="1" t="s">
         <v>106</v>
       </c>
@@ -2023,7 +2018,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2055,7 +2050,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -2084,7 +2079,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>120</v>
       </c>
@@ -2116,7 +2111,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2148,7 +2143,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>129</v>
       </c>
@@ -2180,7 +2175,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>133</v>
       </c>
@@ -2212,7 +2207,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -2244,7 +2239,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>143</v>
       </c>
@@ -2270,7 +2265,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>147</v>
       </c>
@@ -2302,7 +2297,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>154</v>
       </c>
@@ -2334,7 +2329,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>160</v>
       </c>
@@ -2366,7 +2361,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -2398,7 +2393,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -2430,7 +2425,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>177</v>
       </c>
@@ -2462,7 +2457,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>184</v>
       </c>
@@ -2494,7 +2489,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>191</v>
       </c>
@@ -2526,7 +2521,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -2558,7 +2553,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -2590,7 +2585,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>206</v>
       </c>
@@ -2622,7 +2617,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>214</v>
       </c>
@@ -2654,7 +2649,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -2686,7 +2681,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -2718,7 +2713,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>227</v>
       </c>
@@ -2750,7 +2745,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>230</v>
       </c>
@@ -2782,7 +2777,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>233</v>
       </c>
@@ -2814,7 +2809,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>237</v>
       </c>
@@ -2846,7 +2841,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>240</v>
       </c>
@@ -2872,7 +2867,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>243</v>
       </c>
@@ -2904,7 +2899,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>248</v>
       </c>
@@ -2936,7 +2931,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>255</v>
       </c>
@@ -2968,7 +2963,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>260</v>
       </c>
@@ -3000,7 +2995,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>265</v>
       </c>
@@ -3032,7 +3027,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>268</v>
       </c>
@@ -3064,7 +3059,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>272</v>
       </c>
@@ -3096,7 +3091,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>277</v>
       </c>
@@ -3128,7 +3123,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>282</v>
       </c>
@@ -3160,7 +3155,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>285</v>
       </c>
@@ -3192,7 +3187,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>289</v>
       </c>
@@ -3224,7 +3219,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -3256,7 +3251,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>296</v>
       </c>
@@ -3288,7 +3283,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>300</v>
       </c>
@@ -3320,7 +3315,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>305</v>
       </c>
@@ -3352,7 +3347,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>309</v>
       </c>
@@ -3384,7 +3379,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>312</v>
       </c>
@@ -3416,7 +3411,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>316</v>
       </c>
@@ -3448,7 +3443,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>319</v>
       </c>
@@ -3480,7 +3475,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>323</v>
       </c>
@@ -3512,7 +3507,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -3544,7 +3539,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>305</v>
       </c>

--- a/IrregularVerbs-Ahorcado/irregular_verbs_full_list.xlsx
+++ b/IrregularVerbs-Ahorcado/irregular_verbs_full_list.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Valentina\Documents\_La.Miranda\_definitivos\GitHub\LucYago_Games\Irregular-Verbs-iPhone-AHORCADO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12480"/>
   </bookViews>
   <sheets>
     <sheet name="Verbs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1177,8 +1182,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1526,9 +1531,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1541,7 +1546,7 @@
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1605,7 +1610,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1">
+    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1637,7 +1642,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1669,7 +1674,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -1701,7 +1706,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -1733,7 +1738,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>52</v>
       </c>
@@ -1765,7 +1770,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -1797,7 +1802,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>66</v>
       </c>
@@ -1829,7 +1834,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>74</v>
       </c>
@@ -1861,7 +1866,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
@@ -1890,7 +1895,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>87</v>
       </c>
@@ -1922,7 +1927,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>95</v>
       </c>
@@ -1954,7 +1959,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>101</v>
       </c>
@@ -1986,7 +1991,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1">
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>106</v>
       </c>
@@ -2018,7 +2023,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -2050,7 +2055,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>116</v>
       </c>
@@ -2079,7 +2084,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>120</v>
       </c>
@@ -2111,7 +2116,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2143,7 +2148,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>129</v>
       </c>
@@ -2175,7 +2180,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>133</v>
       </c>
@@ -2207,7 +2212,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -2239,7 +2244,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>143</v>
       </c>
@@ -2265,7 +2270,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>147</v>
       </c>
@@ -2297,7 +2302,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>154</v>
       </c>
@@ -2329,7 +2334,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>160</v>
       </c>
@@ -2361,7 +2366,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -2393,7 +2398,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -2425,7 +2430,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>177</v>
       </c>
@@ -2457,7 +2462,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>184</v>
       </c>
@@ -2489,7 +2494,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>191</v>
       </c>
@@ -2521,7 +2526,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -2553,7 +2558,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -2585,7 +2590,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>206</v>
       </c>
@@ -2617,7 +2622,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>214</v>
       </c>
@@ -2649,7 +2654,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -2681,7 +2686,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -2713,7 +2718,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>227</v>
       </c>
@@ -2745,7 +2750,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>230</v>
       </c>
@@ -2777,7 +2782,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>233</v>
       </c>
@@ -2809,7 +2814,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>237</v>
       </c>
@@ -2841,7 +2846,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>240</v>
       </c>
@@ -2867,7 +2872,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>243</v>
       </c>
@@ -2899,7 +2904,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>248</v>
       </c>
@@ -2931,7 +2936,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>255</v>
       </c>
@@ -2963,7 +2968,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>260</v>
       </c>
@@ -2995,7 +3000,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>265</v>
       </c>
@@ -3027,7 +3032,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>268</v>
       </c>
@@ -3059,7 +3064,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>272</v>
       </c>
@@ -3091,7 +3096,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>277</v>
       </c>
@@ -3123,7 +3128,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>282</v>
       </c>
@@ -3155,7 +3160,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>285</v>
       </c>
@@ -3187,7 +3192,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>289</v>
       </c>
@@ -3219,7 +3224,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -3251,7 +3256,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>296</v>
       </c>
@@ -3283,7 +3288,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>300</v>
       </c>
@@ -3315,7 +3320,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>305</v>
       </c>
@@ -3347,7 +3352,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>309</v>
       </c>
@@ -3379,7 +3384,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>312</v>
       </c>
@@ -3411,7 +3416,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>316</v>
       </c>
@@ -3443,7 +3448,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>319</v>
       </c>
@@ -3475,7 +3480,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>323</v>
       </c>
@@ -3507,7 +3512,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -3539,7 +3544,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>305</v>
       </c>
